--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportProcessTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportProcessTemplate.xlsx
@@ -47,7 +47,7 @@
     <t>Lớp số gộp tồn kho</t>
   </si>
   <si>
-    <t>Ngày thứ thực hiện</t>
+    <t xml:space="preserve"> Ngày thứ tự thực hiện </t>
   </si>
 </sst>
 </file>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportProcessTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportProcessTemplate.xlsx
@@ -448,10 +448,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportProcessTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportProcessTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23-kcvn-spm-be\src\main\kotlin\com\kcvn\spm\assets\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KCVN\23-kcvn-spm-be\src\main\kotlin\com\kcvn\spm\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Tên sản phẩm</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Ngày thứ tự thực hiện </t>
+  </si>
+  <si>
+    <t>Tên công đoạn</t>
   </si>
 </sst>
 </file>
@@ -129,7 +132,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -411,30 +414,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AMI1"/>
+  <dimension ref="A1:AMJ1"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="14.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" customWidth="1"/>
-    <col min="11" max="12" width="15" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" customWidth="1"/>
-    <col min="20" max="1023" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="15" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="10" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="1" customWidth="1"/>
+    <col min="21" max="1024" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -442,21 +446,24 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
